--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.6%</t>
+          <t>-195.7%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-120.9%</t>
+          <t>-121.0%</t>
         </is>
       </c>
     </row>
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.457972828628094</v>
+        <v>-3.458462161925382</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.69720150432946</v>
+        <v>1.697005771010545</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2835340181552679</v>
+        <v>0.2830446848579798</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.250867470987607</v>
+        <v>3.250573871009234</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>115.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.6%</t>
+          <t>496.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.4%</t>
+          <t>-531.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-206.5%</t>
+          <t>-216.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-195.7%</t>
+          <t>-219.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-121.0%</t>
+          <t>-135.4%</t>
         </is>
       </c>
     </row>
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.458462161925382</v>
+        <v>-3.698246511227401</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.697005771010545</v>
+        <v>1.601092031289737</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2830446848579798</v>
+        <v>0.04326033555596109</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.250573871009234</v>
+        <v>3.106703261428022</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>115.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.1%</t>
+          <t>496.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-531.4%</t>
+          <t>-532.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-216.1%</t>
+          <t>-216.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.1%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-219.7%</t>
+          <t>-202.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-135.4%</t>
+          <t>-124.9%</t>
         </is>
       </c>
     </row>
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.248061282205574</v>
+        <v>-9.501324475660612</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5359792996255766</v>
+        <v>-0.6372845770075917</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.732839752390036</v>
+        <v>-2.800641109260752</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.523897786136379</v>
+        <v>1.48321697201395</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.978993694438595</v>
+        <v>-9.232256887893632</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.4276837583732913</v>
+        <v>-0.528989035755306</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.463772164623057</v>
+        <v>-2.531573521493773</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.68600684494206</v>
+        <v>1.645326030819631</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.714933756115798</v>
+        <v>-8.968196949570835</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3353200992059246</v>
+        <v>-0.4366253765879398</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.199712226300261</v>
+        <v>-2.267513583170977</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.831182491773986</v>
+        <v>1.790501677651557</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.007854132610959</v>
+        <v>-8.261117326065998</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.05527528346429023</v>
+        <v>-0.1565805608463053</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.199712226300261</v>
+        <v>-2.267513583170977</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.828395458113685</v>
+        <v>1.787714643991256</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.758213102625007</v>
+        <v>-8.011476296080046</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.04492475241793192</v>
+        <v>-0.05638052496408319</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.950071196314309</v>
+        <v>-2.017872553185025</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.978523699993097</v>
+        <v>1.937842885870668</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.503671203283932</v>
+        <v>-7.75693439673897</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.146108333375119</v>
+        <v>0.04480305599310386</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.695529296973234</v>
+        <v>-1.763330653843949</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.1306156608185</v>
+        <v>2.08993484669607</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.270189981054333</v>
+        <v>-7.523453174509371</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2474252511048105</v>
+        <v>0.1461199737227958</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.462048074743635</v>
+        <v>-1.52984943161435</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.278628822994111</v>
+        <v>2.237948008871682</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.090481450910461</v>
+        <v>-7.343744644365499</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3164164528494005</v>
+        <v>0.2151111754673858</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.404876570580939</v>
+        <v>-1.472677927451654</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.31003951517877</v>
+        <v>2.269358701056341</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.958205977279574</v>
+        <v>-7.211469170734612</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.364694129048782</v>
+        <v>0.2633888516667673</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.272601096950053</v>
+        <v>-1.340402453820768</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.384772286104329</v>
+        <v>2.344091471981899</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.767606302606421</v>
+        <v>-7.02086949606146</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4437490596056799</v>
+        <v>0.3424437822236648</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.0820014222769</v>
+        <v>-1.149802779147615</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.501947151595857</v>
+        <v>2.461266337473428</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.51860650392284</v>
+        <v>-6.771869697377879</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5562553203027711</v>
+        <v>0.454950042920756</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.0820014222769</v>
+        <v>-1.149802779147615</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.514853492819516</v>
+        <v>2.474172678697086</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.624196493695945</v>
+        <v>-6.877459687150983</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3860433947943105</v>
+        <v>0.2847381174122958</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.187591412050004</v>
+        <v>-1.255392768920719</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.323523569356435</v>
+        <v>2.282842755234006</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.642931395814542</v>
+        <v>-6.89619458926958</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4270937758239581</v>
+        <v>0.325788498441943</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.187591412050004</v>
+        <v>-1.255392768920719</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.372067911233521</v>
+        <v>2.331387097111092</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.366193221143729</v>
+        <v>-6.619456414598767</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.541168057678278</v>
+        <v>0.4398627802962629</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.005774750940078</v>
+        <v>-1.073576107810793</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.484536919885471</v>
+        <v>2.443856105763042</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.239300814708659</v>
+        <v>-6.492564008163697</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5832110339988277</v>
+        <v>0.481905756616813</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8788823445050084</v>
+        <v>-0.9466837013757233</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.551958377493035</v>
+        <v>2.511277563370606</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.051713306798733</v>
+        <v>-6.304976500253771</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.6512854250677051</v>
+        <v>0.5499801476856905</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8788823445050084</v>
+        <v>-0.9466837013757233</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.544997765397941</v>
+        <v>2.504316951275513</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.809564913344874</v>
+        <v>-6.062828106799913</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.7626071368303915</v>
+        <v>0.6613018594483768</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8788823445050084</v>
+        <v>-0.9466837013757233</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.559460119779084</v>
+        <v>2.518779305656656</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.746335541576526</v>
+        <v>-5.999598735031564</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.7824310059969259</v>
+        <v>0.6811257286149113</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8788823445050084</v>
+        <v>-0.9466837013757233</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.55399224023828</v>
+        <v>2.513311426115851</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.55984784919952</v>
+        <v>-5.813111042654558</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.8545241769583054</v>
+        <v>0.7532188995762903</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6923946521280021</v>
+        <v>-0.7601960089987171</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.66338294967506</v>
+        <v>2.622702135552631</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.538698650296077</v>
+        <v>-5.791961843751115</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.8706848347570082</v>
+        <v>0.7693795573749935</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6712454532245588</v>
+        <v>-0.7390468100952737</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.683773447254452</v>
+        <v>2.643092633132023</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.294933208312632</v>
+        <v>-5.548196401767671</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.9639717198974367</v>
+        <v>0.8626664425154216</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6712454532245588</v>
+        <v>-0.7390468100952737</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.679554155601503</v>
+        <v>2.638873341479074</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.030905141119372</v>
+        <v>-5.28416833457441</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.071707260694757</v>
+        <v>0.9704019833127417</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4693800544086052</v>
+        <v>-0.5371814112793202</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.802797708811091</v>
+        <v>2.762116894688662</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.781054747170297</v>
+        <v>-5.034317940625336</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.164389493258089</v>
+        <v>1.063084215876074</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4693800544086052</v>
+        <v>-0.5371814112793202</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.795539783794793</v>
+        <v>2.754858969672364</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.477487258166319</v>
+        <v>-4.730750451621357</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.289415612380329</v>
+        <v>1.188110334998314</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4693800544086052</v>
+        <v>-0.5371814112793202</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.799138907315442</v>
+        <v>2.758458093193012</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.404007349314305</v>
+        <v>-4.657270542769343</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.332135081975688</v>
+        <v>1.230829804593673</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3959001455565908</v>
+        <v>-0.4637015024273058</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.856554358681204</v>
+        <v>2.815873544558775</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.178974349645482</v>
+        <v>-4.43223754310052</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.421168759459515</v>
+        <v>1.319863482077499</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.170867145887768</v>
+        <v>-0.2386685027584829</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.990594636098795</v>
+        <v>2.949913821976366</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.964339972009075</v>
+        <v>-4.217603165464113</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.511717311568395</v>
+        <v>1.41041203418638</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.04376723174863884</v>
+        <v>-0.02403412512207614</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.124070063734956</v>
+        <v>3.083389249612527</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.697739615034723</v>
+        <v>-3.951002808489761</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.599551713141931</v>
+        <v>1.498246435759916</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.04376723174863884</v>
+        <v>-0.02403412512207614</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.105264322518752</v>
+        <v>3.064583508396323</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.43259493950329</v>
+        <v>3.42628496661634</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.698246511227401</v>
+        <v>-3.708805922320316</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.601092031289737</v>
+        <v>1.596868266852571</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.04326033555596109</v>
+        <v>0.2181627610473693</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.106703261428022</v>
+        <v>3.211644716722867</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-202.2%</t>
+          <t>-202.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-124.9%</t>
+          <t>-166.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1925"/>
+  <dimension ref="A1:G1926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.501324475660612</v>
+        <v>-9.499655622763253</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6372845770075917</v>
+        <v>-0.6366170358486483</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.800641109260752</v>
+        <v>-2.799685038423562</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.48321697201395</v>
+        <v>1.483790614516264</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.232256887893632</v>
+        <v>-9.230588034996273</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.528989035755306</v>
+        <v>-0.5283214945963626</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.531573521493773</v>
+        <v>-2.530617450656583</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.645326030819631</v>
+        <v>1.645899673321945</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.968196949570835</v>
+        <v>-8.966528096673477</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4366253765879398</v>
+        <v>-0.4359578354289964</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.267513583170977</v>
+        <v>-2.266557512333787</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.790501677651557</v>
+        <v>1.79107532015387</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.261117326065998</v>
+        <v>-8.259448473168639</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1565805608463053</v>
+        <v>-0.1559130196873619</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.267513583170977</v>
+        <v>-2.266557512333787</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.787714643991256</v>
+        <v>1.78828828649357</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.011476296080046</v>
+        <v>-8.009807443182687</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.05638052496408319</v>
+        <v>-0.05571298380513978</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.017872553185025</v>
+        <v>-2.016916482347835</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.937842885870668</v>
+        <v>1.938416528372982</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.75693439673897</v>
+        <v>-7.755265543841611</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.04480305599310386</v>
+        <v>0.04547059715204727</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.763330653843949</v>
+        <v>-1.762374583006759</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.08993484669607</v>
+        <v>2.090508489198384</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.523453174509371</v>
+        <v>-7.521784321612013</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1461199737227958</v>
+        <v>0.1467875148817392</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.52984943161435</v>
+        <v>-1.528893360777161</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.237948008871682</v>
+        <v>2.238521651373996</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.343744644365499</v>
+        <v>-7.34207579146814</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2151111754673858</v>
+        <v>0.2157787166263292</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.472677927451654</v>
+        <v>-1.471721856614465</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.269358701056341</v>
+        <v>2.269932343558654</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.211469170734612</v>
+        <v>-7.209800317837254</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2633888516667673</v>
+        <v>0.2640563928257107</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.340402453820768</v>
+        <v>-1.339446382983578</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.344091471981899</v>
+        <v>2.344665114484213</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.02086949606146</v>
+        <v>-7.019200643164101</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3424437822236648</v>
+        <v>0.3431113233826082</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.149802779147615</v>
+        <v>-1.148846708310425</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.461266337473428</v>
+        <v>2.461839979975742</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.771869697377879</v>
+        <v>-6.77020084448052</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.454950042920756</v>
+        <v>0.4556175840796994</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.149802779147615</v>
+        <v>-1.148846708310425</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.474172678697086</v>
+        <v>2.474746321199401</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.877459687150983</v>
+        <v>-6.875790834253625</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2847381174122958</v>
+        <v>0.2854056585712392</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.255392768920719</v>
+        <v>-1.254436698083529</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.282842755234006</v>
+        <v>2.283416397736319</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.89619458926958</v>
+        <v>-6.894525736372222</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.325788498441943</v>
+        <v>0.3264560396008864</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.255392768920719</v>
+        <v>-1.254436698083529</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.331387097111092</v>
+        <v>2.331960739613406</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.619456414598767</v>
+        <v>-6.617787561701409</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4398627802962629</v>
+        <v>0.4405303214552063</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.073576107810793</v>
+        <v>-1.072620036973603</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.443856105763042</v>
+        <v>2.444429748265356</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.492564008163697</v>
+        <v>-6.490895155266339</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.481905756616813</v>
+        <v>0.4825732977757564</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9466837013757233</v>
+        <v>-0.9457276305385335</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.511277563370606</v>
+        <v>2.51185120587292</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.304976500253771</v>
+        <v>-6.303307647356412</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5499801476856905</v>
+        <v>0.5506476888446339</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9466837013757233</v>
+        <v>-0.9457276305385335</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.504316951275513</v>
+        <v>2.504890593777827</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.062828106799913</v>
+        <v>-6.061159253902554</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6613018594483768</v>
+        <v>0.6619694006073202</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9466837013757233</v>
+        <v>-0.9457276305385335</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.518779305656656</v>
+        <v>2.51935294815897</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.999598735031564</v>
+        <v>-5.997929882134206</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6811257286149113</v>
+        <v>0.6817932697738547</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9466837013757233</v>
+        <v>-0.9457276305385335</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.513311426115851</v>
+        <v>2.513885068618165</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.813111042654558</v>
+        <v>-5.8114421897572</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7532188995762903</v>
+        <v>0.7538864407352337</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7601960089987171</v>
+        <v>-0.7592399381615272</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.622702135552631</v>
+        <v>2.623275778054945</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.791961843751115</v>
+        <v>-5.790292990853756</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7693795573749935</v>
+        <v>0.7700470985339369</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7390468100952737</v>
+        <v>-0.7380907392580839</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.643092633132023</v>
+        <v>2.643666275634337</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.548196401767671</v>
+        <v>-5.546527548870312</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.8626664425154216</v>
+        <v>0.863333983674365</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7390468100952737</v>
+        <v>-0.7380907392580839</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.638873341479074</v>
+        <v>2.639446983981387</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.28416833457441</v>
+        <v>-5.282499481677052</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.9704019833127417</v>
+        <v>0.9710695244716852</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.5371814112793202</v>
+        <v>-0.5362253404421303</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.762116894688662</v>
+        <v>2.762690537190976</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.034317940625336</v>
+        <v>-5.032649087727977</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.063084215876074</v>
+        <v>1.063751757035017</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.5371814112793202</v>
+        <v>-0.5362253404421303</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.754858969672364</v>
+        <v>2.755432612174678</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.730750451621357</v>
+        <v>-4.729081598723998</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.188110334998314</v>
+        <v>1.188777876157258</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.5371814112793202</v>
+        <v>-0.5362253404421303</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.758458093193012</v>
+        <v>2.759031735695327</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.657270542769343</v>
+        <v>-4.655601689871984</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.230829804593673</v>
+        <v>1.231497345752617</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4637015024273058</v>
+        <v>-0.4627454315901159</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.815873544558775</v>
+        <v>2.816447187061089</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.43223754310052</v>
+        <v>-4.430568690203161</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.319863482077499</v>
+        <v>1.320531023236443</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2386685027584829</v>
+        <v>-0.2377124319212931</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.949913821976366</v>
+        <v>2.950487464478679</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.217603165464113</v>
+        <v>-4.215934312566755</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.41041203418638</v>
+        <v>1.411079575345323</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.02403412512207614</v>
+        <v>-0.0230780542848863</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.083389249612527</v>
+        <v>3.083962892114841</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.951002808489761</v>
+        <v>-3.949333955592403</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.498246435759916</v>
+        <v>1.498913976918859</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.02403412512207614</v>
+        <v>-0.0230780542848863</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.064583508396323</v>
+        <v>3.065157150898636</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,45 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.42628496661634</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.708805922320316</v>
+        <v>-3.708903458787542</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.596868266852571</v>
+        <v>1.596829252265681</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2181627610473693</v>
+        <v>0.217352442519974</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.211644716722867</v>
+        <v>3.21115852560643</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="2" t="n">
+        <v>45388</v>
+      </c>
+      <c r="B1926" t="n">
+        <v>3.425868567224128</v>
+      </c>
+      <c r="C1926" t="n">
+        <v>2.800720004917751</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>-3.708903458787542</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>1.596829252265681</v>
+      </c>
+      <c r="F1926" t="n">
+        <v>0.217352442519974</v>
+      </c>
+      <c r="G1926" t="n">
+        <v>2.793783801904119</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712295</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.425868567224128</v>
+        <v>3.425868567224126</v>
       </c>
       <c r="C1926" t="n">
         <v>2.800720004917751</v>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,45 +791,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.1%</t>
+          <t>133.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.2%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.3%</t>
+          <t>501.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-532.5%</t>
+          <t>-529.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-216.5%</t>
+          <t>-215.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.6%</t>
+          <t>-131.7%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.613477028535967</v>
+        <v>-6.587026070080381</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4648787166869983</v>
+        <v>0.4754591000692323</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.629197193151051</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.029868902822964</v>
+        <v>-7.003417944367379</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2963160175810766</v>
+        <v>0.3068964009633106</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.629197193151051</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.406545913352809</v>
+        <v>-7.380094954897223</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1559039040378178</v>
+        <v>0.1664842874200518</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.42026077767792</v>
+        <v>-7.393809819222334</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1465175234534684</v>
+        <v>0.1570979068357028</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.7330855769229</v>
+        <v>-7.706634618467314</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.01979252381047747</v>
+        <v>0.03037290719271191</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.737898615388237</v>
+        <v>-7.711447656932651</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.02164628435355098</v>
+        <v>0.03222666773578498</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.630743827853836</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.171247723498473</v>
+        <v>-8.144796765042887</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1557196634249465</v>
+        <v>-0.1451392800427125</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.630743827853836</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.554249112241104</v>
+        <v>-8.527798153785518</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3090223202435833</v>
+        <v>-0.2984419368613489</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.630743827853836</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.929234438412381</v>
+        <v>-8.902783479956796</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4564449347406638</v>
+        <v>-0.4458645513584298</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.005729154025114</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.288764760916383</v>
+        <v>-9.262313802460797</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5949067604442142</v>
+        <v>-0.5843263770619802</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.005729154025114</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.615164789581396</v>
+        <v>-9.58871383112581</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7175507519530422</v>
+        <v>-0.7069703685708078</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.332129182690127</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.608688642787836</v>
+        <v>-9.582237684332251</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7119185426138492</v>
+        <v>-0.7013381592316152</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.325653035896567</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.604997717831425</v>
+        <v>-9.57854675937584</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7104421726312853</v>
+        <v>-0.6998617892490508</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.325653035896567</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.809255893161289</v>
+        <v>-9.782804934705704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7866322456445882</v>
+        <v>-0.7760518622623538</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.453291980510556</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.969894919649654</v>
+        <v>-9.943443961194069</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8464053017554982</v>
+        <v>-0.8358249183732638</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.568025453512952</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.896425087982205</v>
+        <v>-9.86997412952662</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8016456675950976</v>
+        <v>-0.7910652842128632</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.494555621845504</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07154950536875</v>
+        <v>-10.04509854691316</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8571402138021984</v>
+        <v>-0.846559830419964</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.669680039232047</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.30600159938324</v>
+        <v>-10.27955064092765</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9581402163095896</v>
+        <v>-0.947559832927356</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.669680039232047</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.59380544392048</v>
+        <v>-10.56735448546489</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.079933944898462</v>
+        <v>-1.069353561516227</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.957483883769286</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.8236298910843</v>
+        <v>-10.79717893262872</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.170747933925435</v>
+        <v>-1.160167550543201</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.120131420839446</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.05565881082056</v>
+        <v>-11.02920785236498</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.260865773190825</v>
+        <v>-1.250285389808591</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.182144118027869</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.00364329685175</v>
+        <v>-10.97719233839616</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.2360692319169</v>
+        <v>-1.225488848534665</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.182144118027869</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.14531513857587</v>
+        <v>-11.11886418012029</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.294213195505289</v>
+        <v>-1.283632812123055</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.182144118027869</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.24422187903515</v>
+        <v>-11.21777092057956</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.318722481524127</v>
+        <v>-1.308142098141893</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.281050858487145</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.04506977179805</v>
+        <v>-11.01861881334246</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.25211277227597</v>
+        <v>-1.241532388893736</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.115728332537332</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.81922461907864</v>
+        <v>-10.79277366062305</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.152195638151997</v>
+        <v>-1.141615254769764</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.073801656950168</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.53294980675594</v>
+        <v>-10.50649884830036</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.03654656866686</v>
+        <v>-1.025966185284627</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.073801656950168</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58584509480023</v>
+        <v>-10.55939413634464</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.055070909722467</v>
+        <v>-1.044490526340233</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.068846310861722</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.30193636387148</v>
+        <v>-10.27548540541589</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9357737131123312</v>
+        <v>-0.9251933297300976</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.068846310861722</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.05494911367853</v>
+        <v>-10.02849815522294</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8467160754290157</v>
+        <v>-0.8361356920467822</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.82185906066877</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.791112246474457</v>
+        <v>-9.764661288018873</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7510648098602952</v>
+        <v>-0.7404844264780617</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.82185906066877</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.523870445606059</v>
+        <v>-9.497419487150475</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6460026500123099</v>
+        <v>-0.6354222666300764</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.82185906066877</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.499655622763253</v>
+        <v>-9.473204664307669</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6366170358486483</v>
+        <v>-0.6260366524664147</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.799685038423562</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.230588034996273</v>
+        <v>-9.20413707654069</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5283214945963626</v>
+        <v>-0.517741111214129</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.530617450656583</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.966528096673477</v>
+        <v>-8.940077138217893</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4359578354289964</v>
+        <v>-0.4253774520467628</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.266557512333787</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.259448473168639</v>
+        <v>-8.232997514713055</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1559130196873619</v>
+        <v>-0.1453326363051284</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.266557512333787</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.009807443182687</v>
+        <v>-7.983356484727103</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.05571298380513978</v>
+        <v>-0.04513260042290623</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.016916482347835</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.755265543841611</v>
+        <v>-7.728814585386028</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.04547059715204727</v>
+        <v>0.05605098053428081</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.762374583006759</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.521784321612013</v>
+        <v>-7.495333363156429</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1467875148817392</v>
+        <v>0.1573678982639728</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.528893360777161</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.34207579146814</v>
+        <v>-7.315624833012556</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2157787166263292</v>
+        <v>0.2263591000085627</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.471721856614465</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.209800317837254</v>
+        <v>-7.18334935938167</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2640563928257107</v>
+        <v>0.2746367762079442</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.339446382983578</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.019200643164101</v>
+        <v>-6.992749684708517</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3431113233826082</v>
+        <v>0.3536917067648417</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.148846708310425</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.77020084448052</v>
+        <v>-6.743749886024936</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4556175840796994</v>
+        <v>0.466197967461933</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.148846708310425</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.875790834253625</v>
+        <v>-6.849339875798041</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2854056585712392</v>
+        <v>0.2959860419534728</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.254436698083529</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.894525736372222</v>
+        <v>-6.868074777916638</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3264560396008864</v>
+        <v>0.33703642298312</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.254436698083529</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.617787561701409</v>
+        <v>-6.591336603245825</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4405303214552063</v>
+        <v>0.4511107048374399</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.072620036973603</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.490895155266339</v>
+        <v>-6.464444196810755</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4825732977757564</v>
+        <v>0.49315368115799</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.9457276305385335</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.303307647356412</v>
+        <v>-6.276856688900828</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5506476888446339</v>
+        <v>0.5612280722268674</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.9457276305385335</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.061159253902554</v>
+        <v>-6.03470829544697</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6619694006073202</v>
+        <v>0.6725497839895538</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.9457276305385335</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.997929882134206</v>
+        <v>-5.971478923678622</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6817932697738547</v>
+        <v>0.6923736531560882</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.9457276305385335</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.8114421897572</v>
+        <v>-5.784991231301616</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7538864407352337</v>
+        <v>0.7644668241174672</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.7592399381615272</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.790292990853756</v>
+        <v>-5.763842032398172</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7700470985339369</v>
+        <v>0.7806274819161705</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.7380907392580839</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.546527548870312</v>
+        <v>-5.520076590414728</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.863333983674365</v>
+        <v>0.8739143670565985</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.7380907392580839</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.282499481677052</v>
+        <v>-5.256048523221468</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.9710695244716852</v>
+        <v>0.9816499078539187</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.5362253404421303</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.032649087727977</v>
+        <v>-5.006198129272393</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.063751757035017</v>
+        <v>1.074332140417251</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.5362253404421303</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.729081598723998</v>
+        <v>-4.702630640268414</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.188777876157258</v>
+        <v>1.199358259539491</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.5362253404421303</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.655601689871984</v>
+        <v>-4.6291507314164</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.231497345752617</v>
+        <v>1.24207772913485</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.4627454315901159</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.430568690203161</v>
+        <v>-4.404117731747577</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.320531023236443</v>
+        <v>1.331111406618676</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.2377124319212931</v>
@@ -45780,10 +45780,10 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.215934312566755</v>
+        <v>-4.189483354111171</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.411079575345323</v>
+        <v>1.421659958727556</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.0230780542848863</v>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.949333955592403</v>
+        <v>-3.922882997136819</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.498913976918859</v>
+        <v>1.509494360301093</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.0230780542848863</v>
@@ -45826,10 +45826,10 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.708903458787542</v>
+        <v>-3.682452500331959</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.596829252265681</v>
+        <v>1.607409635647914</v>
       </c>
       <c r="F1925" t="n">
         <v>0.217352442519974</v>
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.425868567224126</v>
+        <v>3.802650888578937</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.800720004917751</v>
+        <v>3.150133666082668</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.708903458787542</v>
+        <v>-3.682452500331959</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.596829252265681</v>
+        <v>1.607409635647914</v>
       </c>
       <c r="F1926" t="n">
         <v>0.217352442519974</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.793783801904119</v>
+        <v>3.143197463069036</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.8%</t>
+          <t>133.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-53.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-71.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.6%</t>
+          <t>501.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-529.8%</t>
+          <t>-505.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-215.5%</t>
+          <t>-205.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-156.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-202.3%</t>
+          <t>-195.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-131.7%</t>
+          <t>-120.5%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.587026070080381</v>
+        <v>-6.577414896535662</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4754591000692323</v>
+        <v>0.4793035694871204</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.629197193151051</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.003417944367379</v>
+        <v>-6.993806770822659</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3068964009633106</v>
+        <v>0.3107408703811987</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.629197193151051</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.380094954897223</v>
+        <v>-7.370483781352504</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1664842874200518</v>
+        <v>0.1703287568379399</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.393809819222334</v>
+        <v>-7.384198645677615</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.1570979068357028</v>
+        <v>0.1609423762535904</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.706634618467314</v>
+        <v>-7.697023444922594</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.03037290719271191</v>
+        <v>0.03421737661059954</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.711447656932651</v>
+        <v>-7.701836483387932</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.03222666773578498</v>
+        <v>0.03607113715367305</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.630743827853836</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.144796765042887</v>
+        <v>-8.135185591498168</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1451392800427125</v>
+        <v>-0.1412948106248244</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.630743827853836</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.527798153785518</v>
+        <v>-8.518186980240799</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.2984419368613489</v>
+        <v>-0.2945974674434613</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.630743827853836</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.902783479956796</v>
+        <v>-8.893172306412076</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4458645513584298</v>
+        <v>-0.4420200819405418</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.005729154025114</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.262313802460797</v>
+        <v>-9.252702628916078</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5843263770619802</v>
+        <v>-0.5804819076440921</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.005729154025114</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.58871383112581</v>
+        <v>-9.579102657581091</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7069703685708078</v>
+        <v>-0.7031258991529201</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.332129182690127</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.582237684332251</v>
+        <v>-9.572626510787531</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7013381592316152</v>
+        <v>-0.6974936898137272</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.325653035896567</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.57854675937584</v>
+        <v>-9.56893558583112</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6998617892490508</v>
+        <v>-0.6960173198311632</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.325653035896567</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.782804934705704</v>
+        <v>-9.773193761160984</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7760518622623538</v>
+        <v>-0.7722073928444662</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.453291980510556</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.943443961194069</v>
+        <v>-9.933832787649349</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8358249183732638</v>
+        <v>-0.8319804489553762</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.568025453512952</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.86997412952662</v>
+        <v>-9.8603629559819</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7910652842128632</v>
+        <v>-0.7872208147949755</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.494555621845504</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.04509854691316</v>
+        <v>-10.03548737336844</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.846559830419964</v>
+        <v>-0.8427153610020763</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.669680039232047</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.27955064092765</v>
+        <v>-10.26993946738293</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.947559832927356</v>
+        <v>-0.9437153635094675</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.669680039232047</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.56735448546489</v>
+        <v>-10.55774331192017</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.069353561516227</v>
+        <v>-1.06550909209834</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.957483883769286</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.79717893262872</v>
+        <v>-10.787567759084</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.160167550543201</v>
+        <v>-1.156323081125313</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.120131420839446</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.02920785236498</v>
+        <v>-11.01959667882026</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.250285389808591</v>
+        <v>-1.246440920390703</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.182144118027869</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.97719233839616</v>
+        <v>-10.96758116485145</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.225488848534665</v>
+        <v>-1.221644379116777</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.182144118027869</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.11886418012029</v>
+        <v>-11.10925300657557</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.283632812123055</v>
+        <v>-1.279788342705167</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.182144118027869</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21777092057956</v>
+        <v>-11.20815974703484</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.308142098141893</v>
+        <v>-1.304297628724005</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.281050858487145</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.01861881334246</v>
+        <v>-11.00900763979774</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.241532388893736</v>
+        <v>-1.237687919475848</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.115728332537332</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.79277366062305</v>
+        <v>-10.78316248707833</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.141615254769764</v>
+        <v>-1.137770785351875</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.073801656950168</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.50649884830036</v>
+        <v>-10.49688767475564</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.025966185284627</v>
+        <v>-1.022121715866739</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.073801656950168</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55939413634464</v>
+        <v>-10.54978296279992</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.044490526340233</v>
+        <v>-1.040646056922346</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.068846310861722</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.27548540541589</v>
+        <v>-10.26587423187117</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9251933297300976</v>
+        <v>-0.92134886031221</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.068846310861722</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.02849815522294</v>
+        <v>-10.01888698167822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8361356920467822</v>
+        <v>-0.8322912226288945</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.82185906066877</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.764661288018873</v>
+        <v>-9.755050114474153</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7404844264780617</v>
+        <v>-0.736639957060174</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.82185906066877</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.497419487150475</v>
+        <v>-9.487808313605756</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6354222666300764</v>
+        <v>-0.6315777972121883</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.82185906066877</v>
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.473204664307669</v>
+        <v>-9.211999150205271</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6260366524664147</v>
+        <v>-0.5215544468254554</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.799685038423562</v>
+        <v>-2.732839752390036</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.483790614516264</v>
+        <v>1.523897786136379</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.20413707654069</v>
+        <v>-8.942931562438291</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.517741111214129</v>
+        <v>-0.4132589055731697</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.530617450656583</v>
+        <v>-2.463772164623057</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.645899673321945</v>
+        <v>1.68600684494206</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.940077138217893</v>
+        <v>-8.678871624115494</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4253774520467628</v>
+        <v>-0.3208952464058035</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.266557512333787</v>
+        <v>-2.199712226300261</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.79107532015387</v>
+        <v>1.831182491773986</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.232997514713055</v>
+        <v>-7.971792000610656</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.1453326363051284</v>
+        <v>-0.04085043066416905</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.266557512333787</v>
+        <v>-2.199712226300261</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.78828828649357</v>
+        <v>1.828395458113685</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.983356484727103</v>
+        <v>-7.722150970624704</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.04513260042290623</v>
+        <v>0.0593496052180531</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.016916482347835</v>
+        <v>-1.950071196314309</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.938416528372982</v>
+        <v>1.978523699993097</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.728814585386028</v>
+        <v>-7.467609071283629</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.05605098053428081</v>
+        <v>0.1605331861752402</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.762374583006759</v>
+        <v>-1.695529296973234</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.090508489198384</v>
+        <v>2.1306156608185</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.495333363156429</v>
+        <v>-7.234127849054031</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1573678982639728</v>
+        <v>0.2618501039049321</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.528893360777161</v>
+        <v>-1.462048074743635</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.238521651373996</v>
+        <v>2.278628822994111</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.315624833012556</v>
+        <v>-7.054419318910158</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2263591000085627</v>
+        <v>0.3308413056495221</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.471721856614465</v>
+        <v>-1.404876570580939</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.269932343558654</v>
+        <v>2.31003951517877</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.18334935938167</v>
+        <v>-6.922143845279272</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2746367762079442</v>
+        <v>0.3791189818489036</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.339446382983578</v>
+        <v>-1.272601096950053</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.344665114484213</v>
+        <v>2.384772286104329</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.992749684708517</v>
+        <v>-6.731544170606119</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3536917067648417</v>
+        <v>0.4581739124058011</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.148846708310425</v>
+        <v>-1.0820014222769</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.461839979975742</v>
+        <v>2.501947151595857</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.743749886024936</v>
+        <v>-6.482544371922538</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.466197967461933</v>
+        <v>0.5706801731028923</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.148846708310425</v>
+        <v>-1.0820014222769</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.474746321199401</v>
+        <v>2.514853492819516</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.849339875798041</v>
+        <v>-6.588134361695642</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2959860419534728</v>
+        <v>0.4004682475944321</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.254436698083529</v>
+        <v>-1.187591412050004</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.283416397736319</v>
+        <v>2.323523569356435</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.868074777916638</v>
+        <v>-6.606869263814239</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.33703642298312</v>
+        <v>0.4415186286240793</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.254436698083529</v>
+        <v>-1.187591412050004</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.331960739613406</v>
+        <v>2.372067911233521</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.591336603245825</v>
+        <v>-6.330131089143427</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4511107048374399</v>
+        <v>0.5555929104783992</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.072620036973603</v>
+        <v>-1.005774750940078</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.444429748265356</v>
+        <v>2.484536919885471</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.464444196810755</v>
+        <v>-6.203238682708356</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.49315368115799</v>
+        <v>0.5976358867989493</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.9457276305385335</v>
+        <v>-0.8788823445050084</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.51185120587292</v>
+        <v>2.551958377493035</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.276856688900828</v>
+        <v>-6.01565117479843</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5612280722268674</v>
+        <v>0.6657102778678268</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.9457276305385335</v>
+        <v>-0.8788823445050084</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.504890593777827</v>
+        <v>2.544997765397941</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.03470829544697</v>
+        <v>-5.773502781344572</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6725497839895538</v>
+        <v>0.7770319896305131</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.9457276305385335</v>
+        <v>-0.8788823445050084</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.51935294815897</v>
+        <v>2.559460119779084</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.971478923678622</v>
+        <v>-5.710273409576224</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6923736531560882</v>
+        <v>0.7968558587970476</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.9457276305385335</v>
+        <v>-0.8788823445050084</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.513885068618165</v>
+        <v>2.55399224023828</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.784991231301616</v>
+        <v>-5.523785717199218</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7644668241174672</v>
+        <v>0.8689490297584266</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.7592399381615272</v>
+        <v>-0.6923946521280021</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.623275778054945</v>
+        <v>2.66338294967506</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.763842032398172</v>
+        <v>-5.502636518295774</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7806274819161705</v>
+        <v>0.8851096875571298</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.7380907392580839</v>
+        <v>-0.6712454532245588</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.643666275634337</v>
+        <v>2.683773447254452</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.520076590414728</v>
+        <v>-5.25887107631233</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.8739143670565985</v>
+        <v>0.9783965726975579</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.7380907392580839</v>
+        <v>-0.6712454532245588</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.639446983981387</v>
+        <v>2.679554155601503</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.256048523221468</v>
+        <v>-4.994843009119069</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.9816499078539187</v>
+        <v>1.086132113494878</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.5362253404421303</v>
+        <v>-0.4693800544086052</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.762690537190976</v>
+        <v>2.802797708811091</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.006198129272393</v>
+        <v>-4.744992615169995</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.074332140417251</v>
+        <v>1.17881434605821</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.5362253404421303</v>
+        <v>-0.4693800544086052</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.755432612174678</v>
+        <v>2.795539783794793</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.702630640268414</v>
+        <v>-4.441425126166016</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.199358259539491</v>
+        <v>1.30384046518045</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.5362253404421303</v>
+        <v>-0.4693800544086052</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.759031735695327</v>
+        <v>2.799138907315442</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.6291507314164</v>
+        <v>-4.367945217314002</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.24207772913485</v>
+        <v>1.34655993477581</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4627454315901159</v>
+        <v>-0.3959001455565908</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.816447187061089</v>
+        <v>2.856554358681204</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.404117731747577</v>
+        <v>-4.142912217645179</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.331111406618676</v>
+        <v>1.435593612259636</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2377124319212931</v>
+        <v>-0.170867145887768</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.950487464478679</v>
+        <v>2.990594636098795</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.189483354111171</v>
+        <v>-3.928277840008772</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.421659958727556</v>
+        <v>1.526142164368516</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.0230780542848863</v>
+        <v>0.04376723174863884</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.083962892114841</v>
+        <v>3.124070063734956</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.922882997136819</v>
+        <v>-3.661677483034421</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.509494360301093</v>
+        <v>1.613976565942052</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.0230780542848863</v>
+        <v>0.04376723174863884</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.065157150898636</v>
+        <v>3.105264322518752</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712295</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.682452500331959</v>
+        <v>-3.42124698622956</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.607409635647914</v>
+        <v>1.711891841288874</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.217352442519974</v>
+        <v>0.2841977285534991</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.21115852560643</v>
+        <v>3.251265697226545</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.802650888578937</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.150133666082668</v>
+        <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.682452500331959</v>
+        <v>-3.441777949394277</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.607409635647914</v>
+        <v>1.707608769857807</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.217352442519974</v>
+        <v>0.2841977285534991</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.143197463069036</v>
+        <v>3.255195011061365</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240406.xlsx
+++ b/tame_output/ON/bt/strategyON_20240406.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-505.8%</t>
+          <t>-505.7%</t>
         </is>
       </c>
     </row>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.441777949394277</v>
+        <v>-3.441665845521481</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.707608769857807</v>
+        <v>1.707653611406926</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2841977285534991</v>
